--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestTradeRegist001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestTradeRegist001.xlsx
@@ -1,18 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr showInkAnnotation="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12465"/>
+    <workbookView windowWidth="22368" windowHeight="9420"/>
   </bookViews>
   <sheets>
-    <sheet name="产品交易信息登记" sheetId="1" r:id="rId1"/>
+    <sheet name="资产交易信息登记" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="3" r:id="rId2"/>
     <sheet name="币种填写规则" sheetId="4" r:id="rId3"/>
     <sheet name="版本号 1.1.1" sheetId="2" r:id="rId4"/>
@@ -97,6 +92,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>1.为使导入成功，所有单元格都必须保持模板原有的格式，如须粘贴数据请使用</t>
     </r>
     <r>
@@ -132,6 +133,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>币种填写规则：代码，如：</t>
     </r>
     <r>
@@ -1247,6 +1254,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">
 1.“币种”修改填写格式，由下拉框改为文本输入形式，格式由“01 人民币(CNY)”更改为“CNY”</t>
     </r>
@@ -1266,6 +1279,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">
 1.“币种”的选项“09 俄罗斯卢布(RUR)”调整为“09 俄罗斯卢布(RUB)”</t>
     </r>
@@ -1285,6 +1304,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">
 1.“单位成交价格（净价）”、“单位成交价格（全价）”可填写小于0数值</t>
     </r>
@@ -1301,6 +1326,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>1.0.</t>
     </r>
     <r>
@@ -1315,6 +1346,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">
 1.“币种”要素增加“14 </t>
     </r>
@@ -1405,6 +1442,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>1.0.</t>
     </r>
     <r>
@@ -1434,13 +1477,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
     <numFmt numFmtId="178" formatCode="0.00000_);[Red]\(0.00000\)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1449,7 +1496,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1486,35 +1533,169 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color indexed="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="44"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1528,8 +1709,200 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1539,55 +1912,297 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1596,34 +2211,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
@@ -1639,40 +2260,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2007,130 +2666,134 @@
       <a:lstStyle/>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:W2"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="35.75" style="15" customWidth="1"/>
-    <col min="2" max="2" width="15.875" style="15" customWidth="1"/>
-    <col min="3" max="4" width="19.625" style="15" customWidth="1"/>
-    <col min="5" max="5" width="26" style="15" customWidth="1"/>
-    <col min="6" max="6" width="19.625" style="15" customWidth="1"/>
-    <col min="7" max="8" width="24.75" style="15" customWidth="1"/>
-    <col min="9" max="9" width="21.5" style="15" customWidth="1"/>
-    <col min="10" max="11" width="19.625" style="16" customWidth="1"/>
-    <col min="12" max="13" width="19.625" style="15" customWidth="1"/>
-    <col min="14" max="14" width="19.625" style="17" customWidth="1"/>
-    <col min="15" max="15" width="19.625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="26" style="15" customWidth="1"/>
-    <col min="17" max="23" width="19.625" style="15" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="18"/>
+    <col min="1" max="1" width="35.75" style="17" customWidth="1"/>
+    <col min="2" max="2" width="15.8796296296296" style="17" customWidth="1"/>
+    <col min="3" max="4" width="19.6296296296296" style="17" customWidth="1"/>
+    <col min="5" max="5" width="26" style="17" customWidth="1"/>
+    <col min="6" max="6" width="19.6296296296296" style="17" customWidth="1"/>
+    <col min="7" max="8" width="24.75" style="17" customWidth="1"/>
+    <col min="9" max="9" width="21.5" style="17" customWidth="1"/>
+    <col min="10" max="11" width="19.6296296296296" style="18" customWidth="1"/>
+    <col min="12" max="13" width="19.6296296296296" style="17" customWidth="1"/>
+    <col min="14" max="14" width="19.6296296296296" style="19" customWidth="1"/>
+    <col min="15" max="15" width="19.6296296296296" style="17" customWidth="1"/>
+    <col min="16" max="16" width="26" style="17" customWidth="1"/>
+    <col min="17" max="23" width="19.6296296296296" style="17" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="14" customFormat="1">
-      <c r="A1" s="19" t="s">
+    <row r="1" s="16" customFormat="1" spans="1:23">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="P1" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="S1" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="19" t="s">
+      <c r="T1" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="19" t="s">
+      <c r="U1" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="19" t="s">
+      <c r="V1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="19" t="s">
+      <c r="W1" s="21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="V2" s="20"/>
+    <row r="2" spans="1:22">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="V2" s="22"/>
     </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="16">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="折算人民币金额输入值必须大于等于0且必须为n(15,2)格式。" sqref="J2:J65536">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="数量输入值必须大于等于0且必须为n(18,5)格式。" sqref="G2:G65533 G65534:G65536">
+      <formula1>((LEN(G2)-LEN(INT(G2)))&lt;=6)*(LEN(INT(G2))&lt;=13)*(INT(G2)&gt;=0)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值区间-0~999.99999" sqref="N1">
+      <formula1>-999.99999</formula1>
+      <formula2>999.99999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1">
+      <formula1>"01 资产买入,02 资产卖出或到期,03 存入银行存款,04 银行存款到期,05 拆出和逆回购首期,06 拆入和正回购首期,07 拆出和逆回购到期,08 拆入和正回购到期,09 投资资产所得收益,10 投资资产支出,11 其他收入,12 其他支出"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="折算人民币金额输入值必须大于等于0且必须为n(15,2)格式。" sqref="J2:J65536">
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过13位，小数位不可超过5位" sqref="G1">
       <formula1>((LEN(G1)-LEN(INT(G1)))&lt;=6)*(LEN(INT(G1))&lt;=13)*(INT(G1)&gt;=0)*G1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1">
-      <formula1>"01 资产买入,02 资产卖出或到期,03 存入银行存款,04 银行存款到期,05 拆出和逆回购首期,06 拆入和正回购首期,07 拆出和逆回购到期,08 拆入和正回购到期,09 投资资产所得收益,10 投资资产支出,11 其他收入,12 其他支出"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过13位，小数位不可超过5位" sqref="H1">
-      <formula1>"01 公允价值_x0000_02 摊余成本"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E65536">
       <formula1>"01 资产买入,02 资产卖出或到期,03 存入银行存款,04 银行存款到期,05 拆放同业和买入返售首期,06 同业拆入和卖出回购首期,07 拆放同业和买入返售到期,08 同业拆入和卖出回购到期,09 投资资产所得收益,10 投资资产支出,11 其他收入,12 其他支出"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值区间-0~9999999999999.99" sqref="J1:K1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过13位，小数位不可超过5位" sqref="H1"/>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值区间-0~9999999999999.99" sqref="J1:K1">
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
@@ -2140,16 +2803,12 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H65536">
       <formula1>"01 公允价值,02 摊余成本"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="数量输入值必须大于等于0且必须为n(18,5)格式。" sqref="G2:G65533 G65534:G65536">
-      <formula1>((LEN(G2)-LEN(INT(G2)))&lt;=6)*(LEN(INT(G2))&lt;=13)*(INT(G2)&gt;=0)</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值区间-0~999.99999" sqref="N1">
-      <formula1>-999.99999</formula1>
-      <formula2>999.99999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="发生金额输入值必须大于等于0且必须为n(15,2)格式。" sqref="K2:K65536">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="发生金额输入值必须大于等于0且必须为n(15,2)格式。" sqref="K2:K65536">
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P65536">
+      <formula1>"01 住户,02 广义政府,03 非金融企业,04 银行业存款类金融机构,05 银行非存款类金融机构,06 非银行业金融机构,07 银行非保本理财,08 信托公司资管产品,09 证券公司及其子公司资管产品,10 基金管理公司及其子公司专户,11 期货公司及其子公司资管产品,12 保险资管产品,13 金融资产投资公司资管产品,14 公募基金,15 私募基金,16 其他特定目的载体,17 境外,99 其他"</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="单位成交价格（净价）必须为n(17,4)格式。" sqref="L2:L65533 L65534:L65536">
       <formula1>((LEN(L2)-LEN(INT(L2)))&lt;=5)*(LEN(ABS(INT(L2)))&lt;=13)</formula1>
@@ -2157,12 +2816,9 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="单位成交价格（全价）必须为n(17,4)格式。" sqref="M2:M65533 M65534:M65536">
       <formula1>((LEN(M2)-LEN(INT(M2)))&lt;=5)*(LEN(ABS(INT(M2)))&lt;=13)</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="到期收益率%必须为n(8,5)格式。" sqref="N2:N65536">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="到期收益率%必须为n(8,5)格式。" sqref="N2:N65536">
       <formula1>-999.99999</formula1>
       <formula2>999.99999</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P65536">
-      <formula1>"01 住户,02 广义政府,03 非金融企业,04 银行业存款类金融机构,05 银行非存款类金融机构,06 非银行业金融机构,07 银行非保本理财,08 信托公司资管产品,09 证券公司及其子公司资管产品,10 基金管理公司及其子公司专户,11 期货公司及其子公司资管产品,12 保险资管产品,13 金融资产投资公司资管产品,14 公募基金,15 私募基金,16 其他特定目的载体,17 境外,99 其他"</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V1:V65533 V65534:V65536">
       <formula1>(LEN(V1)=8)*(LEN(INT(V1))=8)*(INT(V1)&gt;0)</formula1>
@@ -2175,1472 +2831,1473 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="84.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="48" customHeight="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" ht="48" customHeight="1" spans="1:1">
+      <c r="A1" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="46.5" customHeight="1">
-      <c r="A2" s="13" t="s">
+    <row r="2" ht="46.5" customHeight="1" spans="1:1">
+      <c r="A2" s="15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="39.75" customHeight="1">
-      <c r="A3" s="13" t="s">
+    <row r="3" ht="39.75" customHeight="1" spans="1:1">
+      <c r="A3" s="15" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection password="EC2B" sheet="1" objects="1" scenarios="1"/>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B179"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="18.375" customWidth="1"/>
+    <col min="2" max="2" width="18.3796296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="25"/>
+      <c r="B1" s="11"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="13" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="13" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="13" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="13" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="13" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="13" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="27">
-      <c r="A17" s="10" t="s">
+    <row r="17" ht="28.8" spans="1:2">
+      <c r="A17" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="13" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="13" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="13" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="13" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="13" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="13" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="13" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="27">
-      <c r="A26" s="10" t="s">
+    <row r="26" ht="28.8" spans="1:2">
+      <c r="A26" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="13" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="13" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="13" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="13" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="13" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="13" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="13" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="13" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="13" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="13" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="13" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="27">
-      <c r="A42" s="10" t="s">
+    <row r="42" ht="28.8" spans="1:2">
+      <c r="A42" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="13" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="13" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="13" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="13" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="13" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="13" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="13" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="13" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="13" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="13" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="13" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="13" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="13" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="13" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="13" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="13" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="13" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="10" t="s">
+      <c r="A63" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="13" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="13" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="13" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="13" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="10" t="s">
+      <c r="A69" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="13" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="13" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="13" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="13" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="13" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="13" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="13" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="13" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="13" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="13" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="13" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="13" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="13" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="10" t="s">
+      <c r="A82" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="13" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="13" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="13" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="13" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="10" t="s">
+      <c r="A86" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="13" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="10" t="s">
+      <c r="A87" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="13" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="13" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="10" t="s">
+      <c r="A89" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="13" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="10" t="s">
+      <c r="A90" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="13" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="10" t="s">
+      <c r="A91" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="13" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="10" t="s">
+      <c r="A92" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="13" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="10" t="s">
+      <c r="A93" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="13" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="10" t="s">
+      <c r="A94" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="13" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="10" t="s">
+      <c r="A95" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="13" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="10" t="s">
+      <c r="A96" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="13" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="10" t="s">
+      <c r="A97" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="13" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="13" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="10" t="s">
+      <c r="A99" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="13" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="10" t="s">
+      <c r="A100" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="13" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="10" t="s">
+      <c r="A101" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="13" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="10" t="s">
+      <c r="A102" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="B102" s="11" t="s">
+      <c r="B102" s="13" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="10" t="s">
+      <c r="A103" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="11" t="s">
+      <c r="B103" s="13" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="10" t="s">
+      <c r="A104" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="13" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="10" t="s">
+      <c r="A105" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="B105" s="11" t="s">
+      <c r="B105" s="13" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="10" t="s">
+      <c r="A106" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="B106" s="11" t="s">
+      <c r="B106" s="13" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="10" t="s">
+      <c r="A107" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="B107" s="11" t="s">
+      <c r="B107" s="13" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="10" t="s">
+      <c r="A108" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="13" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="10" t="s">
+      <c r="A109" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="B109" s="13" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="10" t="s">
+      <c r="A110" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="13" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="10" t="s">
+      <c r="A111" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="B111" s="11" t="s">
+      <c r="B111" s="13" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="10" t="s">
+      <c r="A112" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="13" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="10" t="s">
+      <c r="A113" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="B113" s="11" t="s">
+      <c r="B113" s="13" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="10" t="s">
+      <c r="A114" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="B114" s="11" t="s">
+      <c r="B114" s="13" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="10" t="s">
+      <c r="A115" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="B115" s="11" t="s">
+      <c r="B115" s="13" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="10" t="s">
+      <c r="A116" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B116" s="13" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="10" t="s">
+      <c r="A117" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="B117" s="13" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="10" t="s">
+      <c r="A118" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="13" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="10" t="s">
+      <c r="A119" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="B119" s="11" t="s">
+      <c r="B119" s="13" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="10" t="s">
+      <c r="A120" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="B120" s="11" t="s">
+      <c r="B120" s="13" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="10" t="s">
+      <c r="A121" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B121" s="13" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="10" t="s">
+      <c r="A122" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="B122" s="11" t="s">
+      <c r="B122" s="13" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="10" t="s">
+      <c r="A123" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="B123" s="11" t="s">
+      <c r="B123" s="13" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="10" t="s">
+      <c r="A124" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="B124" s="11" t="s">
+      <c r="B124" s="13" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="10" t="s">
+      <c r="A125" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="B125" s="11" t="s">
+      <c r="B125" s="13" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="10" t="s">
+      <c r="A126" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="B126" s="11" t="s">
+      <c r="B126" s="13" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="10" t="s">
+      <c r="A127" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B127" s="13" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="10" t="s">
+      <c r="A128" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B128" s="11" t="s">
+      <c r="B128" s="13" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="10" t="s">
+      <c r="A129" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="B129" s="11" t="s">
+      <c r="B129" s="13" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="10" t="s">
+      <c r="A130" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="B130" s="11" t="s">
+      <c r="B130" s="13" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="10" t="s">
+      <c r="A131" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="B131" s="11" t="s">
+      <c r="B131" s="13" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="10" t="s">
+      <c r="A132" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="B132" s="11" t="s">
+      <c r="B132" s="13" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="10" t="s">
+      <c r="A133" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="B133" s="11" t="s">
+      <c r="B133" s="13" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="10" t="s">
+      <c r="A134" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="B134" s="11" t="s">
+      <c r="B134" s="13" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="10" t="s">
+      <c r="A135" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="B135" s="11" t="s">
+      <c r="B135" s="13" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="10" t="s">
+      <c r="A136" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="B136" s="11" t="s">
+      <c r="B136" s="13" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="27">
-      <c r="A137" s="10" t="s">
+    <row r="137" ht="28.8" spans="1:2">
+      <c r="A137" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="B137" s="11" t="s">
+      <c r="B137" s="13" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="10" t="s">
+      <c r="A138" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="B138" s="11" t="s">
+      <c r="B138" s="13" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="10" t="s">
+      <c r="A139" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="B139" s="11" t="s">
+      <c r="B139" s="13" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="10" t="s">
+      <c r="A140" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="B140" s="11" t="s">
+      <c r="B140" s="13" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="10" t="s">
+      <c r="A141" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="B141" s="11" t="s">
+      <c r="B141" s="13" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="10" t="s">
+      <c r="A142" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="B142" s="11" t="s">
+      <c r="B142" s="13" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="10" t="s">
+      <c r="A143" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="B143" s="11" t="s">
+      <c r="B143" s="13" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="10" t="s">
+      <c r="A144" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="B144" s="11" t="s">
+      <c r="B144" s="13" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="10" t="s">
+      <c r="A145" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="B145" s="11" t="s">
+      <c r="B145" s="13" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="10" t="s">
+      <c r="A146" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="B146" s="11" t="s">
+      <c r="B146" s="13" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="10" t="s">
+      <c r="A147" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="B147" s="11" t="s">
+      <c r="B147" s="13" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="10" t="s">
+      <c r="A148" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="B148" s="11" t="s">
+      <c r="B148" s="13" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="10" t="s">
+      <c r="A149" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="B149" s="11" t="s">
+      <c r="B149" s="13" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="10" t="s">
+      <c r="A150" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="B150" s="11" t="s">
+      <c r="B150" s="13" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="10" t="s">
+      <c r="A151" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="B151" s="11" t="s">
+      <c r="B151" s="13" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="10" t="s">
+      <c r="A152" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="B152" s="11" t="s">
+      <c r="B152" s="13" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="10" t="s">
+      <c r="A153" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B153" s="11" t="s">
+      <c r="B153" s="13" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="10" t="s">
+      <c r="A154" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="B154" s="11" t="s">
+      <c r="B154" s="13" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="10" t="s">
+      <c r="A155" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B155" s="11" t="s">
+      <c r="B155" s="13" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="10" t="s">
+      <c r="A156" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="B156" s="11" t="s">
+      <c r="B156" s="13" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="10" t="s">
+      <c r="A157" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="B157" s="11" t="s">
+      <c r="B157" s="13" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="10" t="s">
+      <c r="A158" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B158" s="11" t="s">
+      <c r="B158" s="13" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="27">
-      <c r="A159" s="10" t="s">
+    <row r="159" ht="28.8" spans="1:2">
+      <c r="A159" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="B159" s="11" t="s">
+      <c r="B159" s="13" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="10" t="s">
+      <c r="A160" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="B160" s="11" t="s">
+      <c r="B160" s="13" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="10" t="s">
+      <c r="A161" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="B161" s="11" t="s">
+      <c r="B161" s="13" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="27">
-      <c r="A162" s="10" t="s">
+    <row r="162" ht="28.8" spans="1:2">
+      <c r="A162" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="B162" s="11" t="s">
+      <c r="B162" s="13" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="27">
-      <c r="A163" s="10" t="s">
+    <row r="163" ht="28.8" spans="1:2">
+      <c r="A163" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B163" s="11" t="s">
+      <c r="B163" s="13" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="27">
-      <c r="A164" s="10" t="s">
+    <row r="164" ht="28.8" spans="1:2">
+      <c r="A164" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="B164" s="11" t="s">
+      <c r="B164" s="13" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="27">
-      <c r="A165" s="10" t="s">
+    <row r="165" ht="28.8" spans="1:2">
+      <c r="A165" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="B165" s="11" t="s">
+      <c r="B165" s="13" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="10" t="s">
+      <c r="A166" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="B166" s="11" t="s">
+      <c r="B166" s="13" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="27">
-      <c r="A167" s="10" t="s">
+    <row r="167" ht="28.8" spans="1:2">
+      <c r="A167" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="B167" s="11" t="s">
+      <c r="B167" s="13" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="27">
-      <c r="A168" s="10" t="s">
+    <row r="168" ht="28.8" spans="1:2">
+      <c r="A168" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="B168" s="11" t="s">
+      <c r="B168" s="13" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="10" t="s">
+      <c r="A169" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="B169" s="11" t="s">
+      <c r="B169" s="13" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="27">
-      <c r="A170" s="10" t="s">
+    <row r="170" ht="28.8" spans="1:2">
+      <c r="A170" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="B170" s="11" t="s">
+      <c r="B170" s="13" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="10" t="s">
+      <c r="A171" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="B171" s="11" t="s">
+      <c r="B171" s="13" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="10" t="s">
+      <c r="A172" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="B172" s="11" t="s">
+      <c r="B172" s="13" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="10" t="s">
+      <c r="A173" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="B173" s="11" t="s">
+      <c r="B173" s="13" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="10" t="s">
+    <row r="174" ht="28.8" spans="1:2">
+      <c r="A174" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="B174" s="11" t="s">
+      <c r="B174" s="13" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="10" t="s">
+      <c r="A175" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="B175" s="11" t="s">
+      <c r="B175" s="13" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="10" t="s">
+      <c r="A176" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="B176" s="11" t="s">
+      <c r="B176" s="13" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="10" t="s">
+      <c r="A177" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="B177" s="11" t="s">
+      <c r="B177" s="13" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="10" t="s">
+      <c r="A178" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="B178" s="11" t="s">
+      <c r="B178" s="13" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="10" t="s">
+      <c r="A179" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="B179" s="11" t="s">
+      <c r="B179" s="13" t="s">
         <v>382</v>
       </c>
     </row>
@@ -3648,19 +4305,20 @@
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="9.25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="78.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="78.8796296296296" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3679,7 +4337,7 @@
         <v>44512</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="54">
+    <row r="3" ht="57.6" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>386</v>
       </c>
@@ -3703,7 +4361,7 @@
         <v>43683</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="175.5">
+    <row r="6" ht="187.2" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>386</v>
       </c>
@@ -3711,7 +4369,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16.5" customHeight="1">
+    <row r="8" ht="16.5" customHeight="1" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>383</v>
       </c>
@@ -3719,7 +4377,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="1" customFormat="1">
+    <row r="9" s="1" customFormat="1" spans="1:2">
       <c r="A9" s="6" t="s">
         <v>385</v>
       </c>
@@ -3727,7 +4385,7 @@
         <v>43126</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="67.5">
+    <row r="10" ht="72" spans="1:2">
       <c r="A10" s="2" t="s">
         <v>386</v>
       </c>
@@ -3735,7 +4393,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="16.5" customHeight="1">
+    <row r="12" ht="16.5" customHeight="1" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>383</v>
       </c>
@@ -3743,7 +4401,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="1" customFormat="1">
+    <row r="13" s="1" customFormat="1" spans="1:2">
       <c r="A13" s="6" t="s">
         <v>385</v>
       </c>
@@ -3751,7 +4409,7 @@
         <v>42685</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="67.5">
+    <row r="14" ht="72" spans="1:2">
       <c r="A14" s="2" t="s">
         <v>386</v>
       </c>
@@ -3759,7 +4417,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="16.5" customHeight="1">
+    <row r="16" ht="16.5" customHeight="1" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>383</v>
       </c>
@@ -3767,7 +4425,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="1" customFormat="1">
+    <row r="17" s="1" customFormat="1" spans="1:2">
       <c r="A17" s="6" t="s">
         <v>385</v>
       </c>
@@ -3775,7 +4433,7 @@
         <v>42398</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="67.5">
+    <row r="18" ht="72" spans="1:2">
       <c r="A18" s="2" t="s">
         <v>386</v>
       </c>
@@ -3783,7 +4441,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16.5" customHeight="1">
+    <row r="20" ht="16.5" customHeight="1" spans="1:2">
       <c r="A20" s="4" t="s">
         <v>383</v>
       </c>
@@ -3791,7 +4449,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="1" customFormat="1">
+    <row r="21" s="1" customFormat="1" spans="1:2">
       <c r="A21" s="6" t="s">
         <v>385</v>
       </c>
@@ -3799,7 +4457,7 @@
         <v>42384</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="94.5">
+    <row r="22" ht="100.8" spans="1:2">
       <c r="A22" s="2" t="s">
         <v>386</v>
       </c>
@@ -3823,7 +4481,7 @@
         <v>42244</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="67.5">
+    <row r="26" ht="86.4" spans="1:2">
       <c r="A26" s="2" t="s">
         <v>386</v>
       </c>
@@ -3839,7 +4497,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="67.5">
+    <row r="29" ht="72" spans="1:2">
       <c r="A29" s="2" t="s">
         <v>386</v>
       </c>
@@ -3848,7 +4506,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
